--- a/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
+++ b/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="278">
   <si>
     <t>テストID</t>
   </si>
@@ -1065,6 +1065,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「富山県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「富山県」が表示された。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Calibri"/>
@@ -1106,6 +1109,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「石川県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「石川県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-022</t>
   </si>
   <si>
@@ -1150,6 +1156,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「福井県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「福井県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-023</t>
   </si>
   <si>
@@ -1194,6 +1203,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「山梨県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山梨県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-024</t>
   </si>
   <si>
@@ -1282,6 +1294,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「岐阜県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「岐阜県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-026</t>
   </si>
   <si>
@@ -1326,6 +1341,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「静岡県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「静岡県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-027</t>
   </si>
   <si>
@@ -1370,6 +1388,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「愛知県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「愛知県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-028</t>
   </si>
   <si>
@@ -1412,6 +1433,9 @@
   </si>
   <si>
     <t>完了画面に遷移し、データベースの都道府県の欄に「三重県」が表示される。</t>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「三重県」が表示された。</t>
   </si>
   <si>
     <t>UT-029</t>
@@ -3914,10 +3938,18 @@
       <c r="H22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="I22" s="5">
+        <v>46171.0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -3937,23 +3969,31 @@
         <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="I23" s="5">
+        <v>46171.0</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>14</v>
@@ -3968,23 +4008,31 @@
         <v>29</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="I24" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>14</v>
@@ -3999,23 +4047,31 @@
         <v>29</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="I25" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>14</v>
@@ -4030,23 +4086,31 @@
         <v>29</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="I26" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>14</v>
@@ -4061,23 +4125,31 @@
         <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="I27" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>14</v>
@@ -4092,23 +4164,31 @@
         <v>29</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="I28" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>14</v>
@@ -4123,23 +4203,31 @@
         <v>29</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="I29" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M29" s="2"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>14</v>
@@ -4154,23 +4242,31 @@
         <v>29</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+      <c r="I30" s="5">
+        <v>46177.0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M30" s="2"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>14</v>
@@ -4185,10 +4281,10 @@
         <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>20</v>
@@ -4201,7 +4297,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>14</v>
@@ -4216,10 +4312,10 @@
         <v>29</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>20</v>
@@ -4232,7 +4328,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>14</v>
@@ -4247,10 +4343,10 @@
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>20</v>
@@ -4263,7 +4359,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>14</v>
@@ -4278,10 +4374,10 @@
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>20</v>
@@ -4294,7 +4390,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>14</v>
@@ -4309,10 +4405,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>20</v>
@@ -4325,7 +4421,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>14</v>
@@ -4340,10 +4436,10 @@
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>20</v>
@@ -4356,7 +4452,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>14</v>
@@ -4371,10 +4467,10 @@
         <v>29</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>20</v>
@@ -4387,7 +4483,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>14</v>
@@ -4402,10 +4498,10 @@
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
@@ -4418,7 +4514,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>14</v>
@@ -4433,10 +4529,10 @@
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
@@ -4449,7 +4545,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>14</v>
@@ -4464,10 +4560,10 @@
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
@@ -4480,7 +4576,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>14</v>
@@ -4495,10 +4591,10 @@
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
@@ -4511,7 +4607,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>14</v>
@@ -4526,10 +4622,10 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>20</v>
@@ -4542,7 +4638,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>14</v>
@@ -4557,10 +4653,10 @@
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>20</v>
@@ -4573,7 +4669,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>14</v>
@@ -4588,10 +4684,10 @@
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>20</v>
@@ -4604,7 +4700,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>14</v>
@@ -4619,10 +4715,10 @@
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>20</v>
@@ -4635,7 +4731,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>14</v>
@@ -4650,10 +4746,10 @@
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -4666,7 +4762,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>14</v>
@@ -4681,10 +4777,10 @@
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>20</v>
@@ -4697,7 +4793,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>14</v>
@@ -4712,10 +4808,10 @@
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
@@ -4728,7 +4824,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>14</v>
@@ -4743,10 +4839,10 @@
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>20</v>
@@ -4759,7 +4855,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>14</v>
@@ -4774,10 +4870,10 @@
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>20</v>
@@ -4790,7 +4886,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>14</v>
@@ -4805,10 +4901,10 @@
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>20</v>
@@ -4821,7 +4917,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>14</v>
@@ -4836,10 +4932,10 @@
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>20</v>
@@ -4852,7 +4948,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>14</v>
@@ -4867,10 +4963,10 @@
         <v>29</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>20</v>
@@ -4934,7 +5030,7 @@
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>43</v>
@@ -5896,13 +5992,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -5910,181 +6006,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -7092,7 +7188,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7100,16 +7196,16 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
@@ -7117,13 +7213,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
@@ -7131,13 +7227,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
@@ -7145,13 +7241,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7">
@@ -7159,13 +7255,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -7173,27 +7269,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -7201,13 +7297,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -7215,13 +7311,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -7229,13 +7325,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13">
@@ -7243,13 +7339,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14">
@@ -7257,13 +7353,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15">
@@ -7271,13 +7367,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16">
@@ -7285,58 +7381,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
+++ b/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="285">
   <si>
     <t>テストID</t>
   </si>
@@ -1482,6 +1482,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「滋賀県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「滋賀県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-030</t>
   </si>
   <si>
@@ -1526,6 +1529,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「京都府」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「京都府」が表示された。</t>
+  </si>
+  <si>
     <t>UT-031</t>
   </si>
   <si>
@@ -1570,6 +1576,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「大阪府」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「大阪府」が表示された。</t>
+  </si>
+  <si>
     <t>UT-032</t>
   </si>
   <si>
@@ -1614,6 +1623,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「兵庫県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「兵庫県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-033</t>
   </si>
   <si>
@@ -1658,6 +1670,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「和歌山県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「和歌山県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-034</t>
   </si>
   <si>
@@ -1702,6 +1717,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「鳥取県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「鳥取県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-035</t>
   </si>
   <si>
@@ -1744,6 +1762,9 @@
   </si>
   <si>
     <t>完了画面に遷移し、データベースの都道府県の欄に「島根県」が表示される。</t>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「島根県」が表示された。</t>
   </si>
   <si>
     <t>UT-036</t>
@@ -4289,15 +4310,23 @@
       <c r="H31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
+      <c r="I31" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>14</v>
@@ -4312,23 +4341,31 @@
         <v>29</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
+      <c r="I32" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>14</v>
@@ -4343,23 +4380,31 @@
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="I33" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>14</v>
@@ -4374,23 +4419,31 @@
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
+      <c r="I34" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M34" s="2"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>14</v>
@@ -4405,23 +4458,31 @@
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
+      <c r="I35" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M35" s="2"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>14</v>
@@ -4436,23 +4497,31 @@
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
+      <c r="I36" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>14</v>
@@ -4467,23 +4536,31 @@
         <v>29</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
+      <c r="I37" s="5">
+        <v>46193.0</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>14</v>
@@ -4498,10 +4575,10 @@
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
@@ -4514,7 +4591,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>14</v>
@@ -4529,10 +4606,10 @@
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
@@ -4545,7 +4622,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>14</v>
@@ -4560,10 +4637,10 @@
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
@@ -4576,7 +4653,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>14</v>
@@ -4591,10 +4668,10 @@
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
@@ -4607,7 +4684,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>14</v>
@@ -4622,10 +4699,10 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>20</v>
@@ -4638,7 +4715,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>14</v>
@@ -4653,10 +4730,10 @@
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>20</v>
@@ -4669,7 +4746,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>14</v>
@@ -4684,10 +4761,10 @@
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>20</v>
@@ -4700,7 +4777,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>14</v>
@@ -4715,10 +4792,10 @@
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>20</v>
@@ -4731,7 +4808,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>14</v>
@@ -4746,10 +4823,10 @@
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -4762,7 +4839,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>14</v>
@@ -4777,10 +4854,10 @@
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>20</v>
@@ -4793,7 +4870,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>14</v>
@@ -4808,10 +4885,10 @@
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
@@ -4824,7 +4901,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>14</v>
@@ -4839,10 +4916,10 @@
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>20</v>
@@ -4855,7 +4932,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>14</v>
@@ -4870,10 +4947,10 @@
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>20</v>
@@ -4886,7 +4963,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>14</v>
@@ -4901,10 +4978,10 @@
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>20</v>
@@ -4917,7 +4994,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>14</v>
@@ -4932,10 +5009,10 @@
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>20</v>
@@ -4948,7 +5025,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>14</v>
@@ -4963,10 +5040,10 @@
         <v>29</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>20</v>
@@ -5030,7 +5107,7 @@
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>43</v>
@@ -5992,13 +6069,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -6006,181 +6083,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -7188,7 +7265,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7196,16 +7273,16 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
@@ -7213,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
@@ -7227,13 +7304,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -7241,13 +7318,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -7255,13 +7332,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
@@ -7269,27 +7346,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -7297,13 +7374,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -7311,13 +7388,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -7325,13 +7402,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13">
@@ -7339,13 +7416,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14">
@@ -7353,13 +7430,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
@@ -7367,13 +7444,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16">
@@ -7381,58 +7458,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
+++ b/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="294">
   <si>
     <t>テストID</t>
   </si>
@@ -1811,6 +1811,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「岡山県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「岡山県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-037</t>
   </si>
   <si>
@@ -1855,6 +1858,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「広島県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「広島県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-038</t>
   </si>
   <si>
@@ -1899,6 +1905,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「山口県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山口県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-039</t>
   </si>
   <si>
@@ -1943,6 +1952,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「徳島県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「徳島県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-040</t>
   </si>
   <si>
@@ -1987,6 +1999,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「愛媛県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「愛媛県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-041</t>
   </si>
   <si>
@@ -2031,6 +2046,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「香川県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「香川県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-042</t>
   </si>
   <si>
@@ -2075,6 +2093,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「高知県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「高知県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-043</t>
   </si>
   <si>
@@ -2119,6 +2140,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「福岡県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「福岡県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-044</t>
   </si>
   <si>
@@ -2161,6 +2185,9 @@
   </si>
   <si>
     <t>完了画面に遷移し、データベースの都道府県の欄に「佐賀県」が表示される。</t>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「佐賀県」が表示された。</t>
   </si>
   <si>
     <t>UT-045</t>
@@ -4583,15 +4610,23 @@
       <c r="H38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
+      <c r="I38" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M38" s="2"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>14</v>
@@ -4606,23 +4641,31 @@
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
+      <c r="I39" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>14</v>
@@ -4637,23 +4680,31 @@
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
+      <c r="I40" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>14</v>
@@ -4668,23 +4719,31 @@
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
+      <c r="I41" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>14</v>
@@ -4699,23 +4758,31 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
+      <c r="I42" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>14</v>
@@ -4730,23 +4797,31 @@
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
+      <c r="I43" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M43" s="2"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>14</v>
@@ -4761,23 +4836,31 @@
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+      <c r="I44" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>14</v>
@@ -4792,23 +4875,31 @@
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
+      <c r="I45" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>14</v>
@@ -4823,23 +4914,31 @@
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
+      <c r="I46" s="5">
+        <v>46200.0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M46" s="2"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>14</v>
@@ -4854,10 +4953,10 @@
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>20</v>
@@ -4870,7 +4969,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>14</v>
@@ -4885,10 +4984,10 @@
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
@@ -4901,7 +5000,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>14</v>
@@ -4916,10 +5015,10 @@
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>20</v>
@@ -4932,7 +5031,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>14</v>
@@ -4947,10 +5046,10 @@
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>20</v>
@@ -4963,7 +5062,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>14</v>
@@ -4978,10 +5077,10 @@
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>20</v>
@@ -4994,7 +5093,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>14</v>
@@ -5009,10 +5108,10 @@
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>20</v>
@@ -5025,7 +5124,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>14</v>
@@ -5040,10 +5139,10 @@
         <v>29</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>20</v>
@@ -5107,7 +5206,7 @@
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>43</v>
@@ -6069,13 +6168,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -6083,181 +6182,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -7265,7 +7364,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7273,16 +7372,16 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -7290,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5">
@@ -7304,13 +7403,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -7318,13 +7417,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
@@ -7332,13 +7431,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
@@ -7346,27 +7445,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -7374,13 +7473,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -7388,13 +7487,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
@@ -7402,13 +7501,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13">
@@ -7416,13 +7515,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14">
@@ -7430,13 +7529,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15">
@@ -7444,13 +7543,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16">
@@ -7458,58 +7557,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
+++ b/Test/ユーザー登録 確認＆完了結合テストケース 実行.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="300">
   <si>
     <t>テストID</t>
   </si>
@@ -2234,6 +2234,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「長崎県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「長崎県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-046</t>
   </si>
   <si>
@@ -2278,6 +2281,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「熊本県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「熊本県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-047</t>
   </si>
   <si>
@@ -2322,6 +2328,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「大分県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「大分県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-048</t>
   </si>
   <si>
@@ -2366,6 +2375,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「宮崎県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「宮崎県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-049</t>
   </si>
   <si>
@@ -2410,6 +2422,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「鹿児島県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「鹿児島県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-050</t>
   </si>
   <si>
@@ -2452,6 +2467,9 @@
   </si>
   <si>
     <t>完了画面に遷移し、データベースの都道府県の欄に「沖縄県」が表示される。</t>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「沖縄県」が表示された。</t>
   </si>
   <si>
     <t>UT-051</t>
@@ -2476,19 +2494,7 @@
 (パスワードに関してはハッシュ化されたものが表示されている。)</t>
   </si>
   <si>
-    <t>"名前（姓）=ひらがな・漢字・10文字以内
-名前（名）=ひらがな・漢字・10文字以内
-カナ（姓）=カタカナ・10文字以内
-カナ（名）=カタカナ・10文字以内
-メールアドレス=半角英数字・半角記号（ハイフン・アットマーク）・100文字以内
-パスワード=半角英数字・10文字以内
-性別＝男か女のどちらかを選択
-郵便番号=半角数字・7文字以内
-住所（都道府県）＝北海道
-住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
-住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
-アカウント権限＝一般か管理者を選択
-（※登録画面にて入力する内容）"</t>
+    <t>完了画面に遷移し、データベースの各々の欄に入力・選択した内容が表示されてた。</t>
   </si>
   <si>
     <t>観点カテゴリ</t>
@@ -2802,7 +2808,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -2830,17 +2836,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left/>
       <top/>
       <bottom/>
@@ -2858,7 +2853,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2877,23 +2872,17 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -4961,15 +4950,23 @@
       <c r="H47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+      <c r="I47" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>14</v>
@@ -4984,23 +4981,31 @@
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
+      <c r="I48" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>14</v>
@@ -5015,23 +5020,31 @@
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
+      <c r="I49" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>14</v>
@@ -5046,23 +5059,31 @@
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
+      <c r="I50" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M50" s="2"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>14</v>
@@ -5077,23 +5098,31 @@
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
+      <c r="I51" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>14</v>
@@ -5108,65 +5137,81 @@
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
+      <c r="I52" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B53" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="H53" s="7" t="s">
+      <c r="F53" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
+      <c r="I53" s="5">
+        <v>46208.0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="2"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -5190,35 +5235,19 @@
     <row r="74" ht="15.75" customHeight="1"/>
     <row r="75" ht="15.75" customHeight="1"/>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
     </row>
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
@@ -6168,13 +6197,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -6182,181 +6211,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -7363,25 +7392,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12"/>
+      <c r="A1" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>249</v>
+      <c r="A3" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -7389,13 +7418,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -7403,13 +7432,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
@@ -7417,13 +7446,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7">
@@ -7431,13 +7460,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -7445,27 +7474,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -7473,13 +7502,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
@@ -7487,13 +7516,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -7501,13 +7530,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
@@ -7515,13 +7544,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14">
@@ -7529,13 +7558,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
@@ -7543,13 +7572,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="16">
@@ -7557,58 +7586,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>287</v>
+      <c r="A18" s="12" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>289</v>
+      <c r="A19" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>290</v>
+      <c r="A20" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>291</v>
+      <c r="A21" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>292</v>
+      <c r="A22" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>293</v>
+      <c r="A23" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
